--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -591,7 +591,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -591,7 +596,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -655,19 +660,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/kartor/S 2223-2021 karta.png", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0186/kartor_geotiff/S 2223-2021 georefererad karta.tif", "S 2223-2021")</f>
+        <v/>
+      </c>
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/klagomål/S 2223-2021 FSC-klagomål.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/klagomålsmail/S 2223-2021 FSC-klagomål mail.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/tillsyn/S 2223-2021 tillsynsbegäran.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/tillsynsmail/S 2223-2021 tillsynsbegäran mail.docx", "S 2223-2021")</f>
         <v/>
       </c>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -522,55 +522,60 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Antal fynd</t>
+          <t>Fynd</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Nya fynd</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>Artnamn</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Artfyndslänk</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Kartlänk</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Geotifflänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -596,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -644,7 +649,10 @@
       <c r="T2" t="n">
         <v>7</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Blekticka
 Rutskinn
@@ -652,31 +660,31 @@
 Hasselticka</t>
         </is>
       </c>
-      <c r="V2">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/artfynd/S 2223-2021 artfynd.xlsx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="W2">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/kartor/S 2223-2021 karta.png", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/kartor_geotiff/S 2223-2021 georefererad karta.tif", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/klagomål/S 2223-2021 FSC-klagomål.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/klagomålsmail/S 2223-2021 FSC-klagomål mail.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/tillsyn/S 2223-2021 tillsynsbegäran.docx", "S 2223-2021")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0186/tillsynsmail/S 2223-2021 tillsynsbegäran mail.docx", "S 2223-2021")</f>
         <v/>
       </c>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt LIDINGÖ.xlsx
+++ b/Översikt LIDINGÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44334</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
